--- a/clean/dic_arg_prev_dm.xlsx
+++ b/clean/dic_arg_prev_dm.xlsx
@@ -423,7 +423,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>grupo_edad_10</t>
+          <t>grupo_edad10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
